--- a/Chapter-6a/2 - OPD - Checklist for Equipment & Furniture Requirements_for HTML.xlsx
+++ b/Chapter-6a/2 - OPD - Checklist for Equipment & Furniture Requirements_for HTML.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Architecture Manual\1 - Final Manual - March - April 2021\Architecture Manual - Sections\Section 6a - Outpatient examination process\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasipriyakarumanchi/Library/CloudStorage/GoogleDrive-sashi@aravind.org/My Drive/Architecture Manual/3 - Final Version - Under Review/Section 6a - Outpatient examination process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6017017-8BF4-4638-8115-3775E4BC8EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09DDD63-5D55-2349-8A8B-F4D3D2DB6707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{1802CD6A-863A-4606-9770-9B19CEF1587F}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20020" xr2:uid="{1802CD6A-863A-4606-9770-9B19CEF1587F}"/>
   </bookViews>
   <sheets>
     <sheet name="OPD - Equipment &amp; Furniture" sheetId="1" r:id="rId1"/>
@@ -40,9 +40,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="100">
   <si>
-    <t>Standardised Architectural Modules</t>
-  </si>
-  <si>
     <t>Room Name</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
     <t>Zywave, Orbscan room (*Zywave Orbscan)</t>
   </si>
   <si>
-    <t>Pentacom room (*Pentacom machine)</t>
-  </si>
-  <si>
     <t>Confocal room (*confocal machine)</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>Typical laser room for retina (* Recommended laser machine)</t>
   </si>
   <si>
-    <t>Ocular Prosthetic</t>
-  </si>
-  <si>
     <t>Exhast fan in the lab</t>
   </si>
   <si>
@@ -208,31 +199,6 @@
     <t>S No</t>
   </si>
   <si>
-    <t>Version: Phase -1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Century Gothic"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Checklist: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Century Gothic"/>
-        <family val="2"/>
-      </rPr>
-      <t>Outpatient Services: Clinical room wise requirements</t>
-    </r>
-  </si>
-  <si>
     <t>Recommendations:</t>
   </si>
   <si>
@@ -246,9 +212,6 @@
   </si>
   <si>
     <t>in feet</t>
-  </si>
-  <si>
-    <t>Squint examination room (* Synoptophore, Triangle table, Loose prism)</t>
   </si>
   <si>
     <t>Equipment / Instruments</t>
@@ -296,9 +259,6 @@
     <t>I</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient regiration &amp; coordination area </t>
-  </si>
-  <si>
     <t>Patient registration</t>
   </si>
   <si>
@@ -338,9 +298,6 @@
     <t xml:space="preserve">Lacrimal exam/suture removal room </t>
   </si>
   <si>
-    <t>Aesthetic cinic</t>
-  </si>
-  <si>
     <t>Assessment area</t>
   </si>
   <si>
@@ -353,8 +310,72 @@
     <t>Hess Diplopia room (*Perimetry, Hess chart)</t>
   </si>
   <si>
+    <t>2.  Computer with LAN connection or wireless connectivity in every room in the patient care area (a default requirement if there is a plan to deploy EMR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.  Display monitors in the waiting area - to display patients queue in EMR eco-system /or for awareness creation; </t>
+  </si>
+  <si>
+    <t>FFA room (*Topcon Zeiss, stretcher)</t>
+  </si>
+  <si>
+    <t>Vision stimulation room (*LCD Screen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting chairs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Fans to be considered in the patient care areas where no AC is provided; </t>
+  </si>
+  <si>
+    <t>Aesthetic clinic</t>
+  </si>
+  <si>
+    <t>Ocular prosthetic room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient registration &amp; coordination area </t>
+  </si>
+  <si>
+    <t>Strabismus examination room (* Synoptophore, Triangle table, Loose prism)</t>
+  </si>
+  <si>
+    <t>To carry out CCL procedure</t>
+  </si>
+  <si>
+    <t>Pachymetry/Pentacom room (*Pentacom machine)</t>
+  </si>
+  <si>
+    <t>ERG room (*ERG machine. cylinder oxygen and crash cart)</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Dimensions </t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="4"/>
+        <rFont val="Century Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Checklist: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Century Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t>Outpatient Services: Clinical room wise requirements</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Standardised Architectural layout modules </t>
+  </si>
+  <si>
+    <r>
+      <t>Dimensions (Optional to include)</t>
     </r>
     <r>
       <rPr>
@@ -364,36 +385,15 @@
         <rFont val="Century Gothic"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">(columns to be deleted) </t>
+      <t xml:space="preserve"> </t>
     </r>
-  </si>
-  <si>
-    <t>2.  Computer with LAN connection or wireless connectivity in every room in the patient care area (a default requirement if there is a plan to deploy EMR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.  Display monitors in the waiting area - to display patients queue in EMR eco-system /or for awareness creation; </t>
-  </si>
-  <si>
-    <t>ERG room (*ERG machine. cylinder oxygen, crash cart)</t>
-  </si>
-  <si>
-    <t>FFA room (*Topcon Zeiss, stretcher)</t>
-  </si>
-  <si>
-    <t>Vision stimulation room (*LCD Screen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting chairs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Fans to be considered in the patient care areas where no AC is provided; </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,13 +465,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -485,6 +478,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="4"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
@@ -538,7 +545,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="76">
+  <borders count="77">
     <border>
       <left/>
       <right/>
@@ -931,26 +938,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -1520,6 +1507,43 @@
       </top>
       <bottom style="double">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1577,7 +1601,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1683,163 +1707,163 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="55" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="55" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="57" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="65" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="66" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1875,27 +1899,51 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1905,61 +1953,37 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1981,9 +2005,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2021,7 +2045,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2127,7 +2151,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2269,7 +2293,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2278,77 +2302,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A6E0EB8-8705-4D08-B32E-8E47B1A803B5}">
   <dimension ref="A1:AN57"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.26171875" style="8" customWidth="1"/>
-    <col min="2" max="2" width="59.20703125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="4.7890625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7890625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="59.1640625" style="1" customWidth="1"/>
+    <col min="3" max="5" width="4.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="4" style="19" customWidth="1"/>
-    <col min="8" max="8" width="5.15625" style="19" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" style="19" customWidth="1"/>
     <col min="9" max="9" width="4" style="19" customWidth="1"/>
-    <col min="10" max="10" width="5.20703125" style="19" customWidth="1"/>
-    <col min="11" max="11" width="8" style="19" customWidth="1"/>
-    <col min="12" max="13" width="3.578125" style="19" customWidth="1"/>
-    <col min="14" max="15" width="3.68359375" style="19" customWidth="1"/>
-    <col min="16" max="17" width="3.3125" style="19" customWidth="1"/>
-    <col min="18" max="19" width="3.3671875" style="19" customWidth="1"/>
-    <col min="20" max="20" width="4.83984375" style="19" customWidth="1"/>
-    <col min="21" max="21" width="3.15625" style="19" customWidth="1"/>
-    <col min="22" max="22" width="3.68359375" style="19" customWidth="1"/>
-    <col min="23" max="23" width="4.5234375" style="19" customWidth="1"/>
-    <col min="24" max="24" width="3.68359375" style="19" customWidth="1"/>
-    <col min="25" max="25" width="3.734375" style="19" customWidth="1"/>
-    <col min="26" max="26" width="5.26171875" style="19" customWidth="1"/>
-    <col min="27" max="27" width="6.15625" style="19" customWidth="1"/>
+    <col min="10" max="10" width="5.1640625" style="19" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" style="19" customWidth="1"/>
+    <col min="12" max="13" width="3.5" style="19" customWidth="1"/>
+    <col min="14" max="15" width="3.6640625" style="19" customWidth="1"/>
+    <col min="16" max="19" width="3.33203125" style="19" customWidth="1"/>
+    <col min="20" max="20" width="4.83203125" style="19" customWidth="1"/>
+    <col min="21" max="21" width="3.1640625" style="19" customWidth="1"/>
+    <col min="22" max="22" width="3.6640625" style="19" customWidth="1"/>
+    <col min="23" max="23" width="4.5" style="19" customWidth="1"/>
+    <col min="24" max="25" width="3.6640625" style="19" customWidth="1"/>
+    <col min="26" max="26" width="5.33203125" style="19" customWidth="1"/>
+    <col min="27" max="27" width="6.1640625" style="19" customWidth="1"/>
     <col min="28" max="28" width="4" style="19" customWidth="1"/>
-    <col min="29" max="29" width="3.5234375" style="19" customWidth="1"/>
-    <col min="30" max="30" width="3.20703125" style="19" customWidth="1"/>
-    <col min="31" max="31" width="3.62890625" style="19" customWidth="1"/>
-    <col min="32" max="32" width="4.62890625" style="19" customWidth="1"/>
-    <col min="33" max="34" width="3.578125" style="19" customWidth="1"/>
-    <col min="35" max="35" width="3.47265625" style="19" customWidth="1"/>
-    <col min="36" max="36" width="3.3671875" style="19" customWidth="1"/>
-    <col min="37" max="37" width="4.47265625" style="5" customWidth="1"/>
-    <col min="38" max="38" width="20.1015625" style="1" customWidth="1"/>
-    <col min="39" max="40" width="8.83984375" style="1"/>
-    <col min="41" max="16384" width="8.83984375" style="6"/>
+    <col min="29" max="29" width="3.5" style="19" customWidth="1"/>
+    <col min="30" max="30" width="3.1640625" style="19" customWidth="1"/>
+    <col min="31" max="31" width="3.6640625" style="19" customWidth="1"/>
+    <col min="32" max="32" width="4.6640625" style="19" customWidth="1"/>
+    <col min="33" max="35" width="3.5" style="19" customWidth="1"/>
+    <col min="36" max="36" width="3.33203125" style="19" customWidth="1"/>
+    <col min="37" max="37" width="4.5" style="5" customWidth="1"/>
+    <col min="38" max="38" width="20.1640625" style="1" customWidth="1"/>
+    <col min="39" max="40" width="8.83203125" style="1"/>
+    <col min="41" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="13" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="140" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="140"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="140"/>
-      <c r="AD1" s="140"/>
-      <c r="AE1" s="140"/>
+    <row r="1" spans="1:40" s="13" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="144" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="144"/>
+      <c r="Z1" s="144"/>
+      <c r="AA1" s="144"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="144"/>
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="144"/>
       <c r="AF1" s="22"/>
       <c r="AG1" s="25"/>
       <c r="AH1" s="22"/>
@@ -2356,81 +2377,79 @@
       <c r="AJ1" s="22"/>
       <c r="AK1" s="22"/>
     </row>
-    <row r="2" spans="1:40" s="12" customFormat="1" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="A2" s="141" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
-      <c r="S2" s="141"/>
-      <c r="T2" s="141"/>
-      <c r="U2" s="141"/>
-      <c r="V2" s="141"/>
-      <c r="W2" s="141"/>
-      <c r="X2" s="141"/>
-      <c r="Y2" s="141"/>
-      <c r="Z2" s="141"/>
-      <c r="AA2" s="141"/>
-      <c r="AB2" s="141"/>
-      <c r="AC2" s="141"/>
-      <c r="AD2" s="141"/>
-      <c r="AE2" s="141"/>
-      <c r="AF2" s="23"/>
-      <c r="AG2" s="8"/>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-    </row>
-    <row r="3" spans="1:40" s="12" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="141" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="141"/>
-      <c r="R3" s="141"/>
-      <c r="S3" s="141"/>
-      <c r="T3" s="141"/>
-      <c r="U3" s="141"/>
-      <c r="V3" s="141"/>
-      <c r="W3" s="141"/>
-      <c r="X3" s="141"/>
-      <c r="Y3" s="141"/>
-      <c r="Z3" s="141"/>
-      <c r="AA3" s="141"/>
-      <c r="AB3" s="141"/>
-      <c r="AC3" s="141"/>
-      <c r="AD3" s="141"/>
-      <c r="AE3" s="141"/>
+    <row r="2" spans="1:40" s="13" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="144" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="144"/>
+      <c r="R2" s="144"/>
+      <c r="S2" s="144"/>
+      <c r="T2" s="144"/>
+      <c r="U2" s="144"/>
+      <c r="V2" s="144"/>
+      <c r="W2" s="144"/>
+      <c r="X2" s="144"/>
+      <c r="Y2" s="144"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="144"/>
+      <c r="AB2" s="144"/>
+      <c r="AC2" s="144"/>
+      <c r="AD2" s="144"/>
+      <c r="AE2" s="144"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="145"/>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="22"/>
+      <c r="AJ2" s="22"/>
+      <c r="AK2" s="22"/>
+    </row>
+    <row r="3" spans="1:40" s="12" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="123"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="123"/>
+      <c r="Q3" s="123"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="123"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
+      <c r="W3" s="123"/>
+      <c r="X3" s="123"/>
+      <c r="Y3" s="123"/>
+      <c r="Z3" s="123"/>
+      <c r="AA3" s="123"/>
+      <c r="AB3" s="123"/>
+      <c r="AC3" s="123"/>
+      <c r="AD3" s="123"/>
+      <c r="AE3" s="123"/>
       <c r="AF3" s="23"/>
       <c r="AG3" s="8"/>
       <c r="AH3" s="23"/>
@@ -2438,187 +2457,187 @@
       <c r="AJ3" s="23"/>
       <c r="AK3" s="23"/>
     </row>
-    <row r="4" spans="1:40" s="37" customFormat="1" ht="27" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="142" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="137" t="s">
+    <row r="4" spans="1:40" s="37" customFormat="1" ht="27" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="124" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="135" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="129" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
+      <c r="S4" s="130"/>
+      <c r="T4" s="130"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="126" t="s">
+        <v>65</v>
+      </c>
+      <c r="W4" s="126"/>
+      <c r="X4" s="126"/>
+      <c r="Y4" s="126"/>
+      <c r="Z4" s="126"/>
+      <c r="AA4" s="127"/>
+      <c r="AB4" s="45"/>
+      <c r="AC4" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="127" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="147" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="148"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="148"/>
-      <c r="K4" s="148"/>
-      <c r="L4" s="148"/>
-      <c r="M4" s="148"/>
-      <c r="N4" s="148"/>
-      <c r="O4" s="148"/>
-      <c r="P4" s="148"/>
-      <c r="Q4" s="148"/>
-      <c r="R4" s="148"/>
-      <c r="S4" s="148"/>
-      <c r="T4" s="148"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="144" t="s">
+      <c r="AD4" s="126"/>
+      <c r="AE4" s="126"/>
+      <c r="AF4" s="126"/>
+      <c r="AG4" s="126"/>
+      <c r="AH4" s="126"/>
+      <c r="AI4" s="126"/>
+      <c r="AJ4" s="126"/>
+      <c r="AK4" s="127"/>
+      <c r="AL4" s="120" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" s="18" customFormat="1" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="125"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="146" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="147"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="56" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="W4" s="144"/>
-      <c r="X4" s="144"/>
-      <c r="Y4" s="144"/>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="145"/>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="146" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD4" s="144"/>
-      <c r="AE4" s="144"/>
-      <c r="AF4" s="144"/>
-      <c r="AG4" s="144"/>
-      <c r="AH4" s="144"/>
-      <c r="AI4" s="144"/>
-      <c r="AJ4" s="144"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="137" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" s="18" customFormat="1" ht="104.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="143"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="124" t="s">
+      <c r="T5" s="54" t="s">
         <v>62</v>
-      </c>
-      <c r="D5" s="125"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="56" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="O5" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="56" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="R5" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="S5" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="T5" s="54" t="s">
-        <v>68</v>
       </c>
       <c r="U5" s="40"/>
       <c r="V5" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="W5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="W5" s="14" t="s">
+      <c r="X5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="X5" s="14" t="s">
+      <c r="Y5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="Y5" s="14" t="s">
+      <c r="Z5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="Z5" s="14" t="s">
+      <c r="AA5" s="16" t="s">
         <v>19</v>
-      </c>
-      <c r="AA5" s="16" t="s">
-        <v>20</v>
       </c>
       <c r="AB5" s="46"/>
       <c r="AC5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="AD5" s="14" t="s">
+      <c r="AE5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="AE5" s="14" t="s">
+      <c r="AF5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AF5" s="14" t="s">
+      <c r="AG5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="AG5" s="14" t="s">
+      <c r="AH5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="AH5" s="14" t="s">
+      <c r="AI5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="AI5" s="14" t="s">
+      <c r="AJ5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="AJ5" s="14" t="s">
+      <c r="AK5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="AK5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="AL5" s="138"/>
-    </row>
-    <row r="6" spans="1:40" s="63" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="AL5" s="121"/>
+    </row>
+    <row r="6" spans="1:40" s="63" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="134" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="135"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="135"/>
-      <c r="O6" s="135"/>
-      <c r="P6" s="135"/>
-      <c r="Q6" s="135"/>
-      <c r="R6" s="135"/>
-      <c r="S6" s="135"/>
-      <c r="T6" s="136"/>
+        <v>66</v>
+      </c>
+      <c r="B6" s="141" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="142"/>
+      <c r="D6" s="142"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="142"/>
+      <c r="I6" s="142"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="142"/>
+      <c r="M6" s="142"/>
+      <c r="N6" s="142"/>
+      <c r="O6" s="142"/>
+      <c r="P6" s="142"/>
+      <c r="Q6" s="142"/>
+      <c r="R6" s="142"/>
+      <c r="S6" s="142"/>
+      <c r="T6" s="143"/>
       <c r="U6" s="61"/>
       <c r="V6" s="62"/>
       <c r="W6" s="62"/>
@@ -2628,12 +2647,12 @@
       <c r="AA6" s="62"/>
       <c r="AL6" s="104"/>
     </row>
-    <row r="7" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>1</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="30"/>
@@ -2652,15 +2671,15 @@
       <c r="Q7" s="24"/>
       <c r="R7" s="24"/>
       <c r="S7" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T7" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U7" s="42"/>
       <c r="V7" s="30"/>
       <c r="W7" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X7" s="21"/>
       <c r="Y7" s="24"/>
@@ -2680,12 +2699,12 @@
       <c r="AM7" s="12"/>
       <c r="AN7" s="12"/>
     </row>
-    <row r="8" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>2</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="30"/>
@@ -2704,7 +2723,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="24"/>
       <c r="S8" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T8" s="35"/>
       <c r="U8" s="42"/>
@@ -2725,17 +2744,17 @@
       <c r="AJ8" s="21"/>
       <c r="AK8" s="28"/>
       <c r="AL8" s="105" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AM8" s="12"/>
       <c r="AN8" s="12"/>
     </row>
-    <row r="9" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>3</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="30"/>
@@ -2754,7 +2773,7 @@
       <c r="Q9" s="24"/>
       <c r="R9" s="24"/>
       <c r="S9" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T9" s="35"/>
       <c r="U9" s="42"/>
@@ -2775,17 +2794,17 @@
       <c r="AJ9" s="21"/>
       <c r="AK9" s="28"/>
       <c r="AL9" s="105" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AM9" s="12"/>
       <c r="AN9" s="12"/>
     </row>
-    <row r="10" spans="1:40" s="86" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:40" s="86" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="71">
         <v>4</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C10" s="73"/>
       <c r="D10" s="74"/>
@@ -2804,7 +2823,7 @@
       <c r="Q10" s="79"/>
       <c r="R10" s="79"/>
       <c r="S10" s="78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T10" s="80"/>
       <c r="U10" s="81"/>
@@ -2825,36 +2844,36 @@
       <c r="AJ10" s="78"/>
       <c r="AK10" s="82"/>
       <c r="AL10" s="105" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="AM10" s="85"/>
       <c r="AN10" s="85"/>
     </row>
-    <row r="11" spans="1:40" s="63" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:40" s="63" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="60" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
-      <c r="N11" s="130"/>
-      <c r="O11" s="130"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="130"/>
-      <c r="R11" s="130"/>
-      <c r="S11" s="130"/>
-      <c r="T11" s="122"/>
+        <v>72</v>
+      </c>
+      <c r="B11" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
+      <c r="L11" s="132"/>
+      <c r="M11" s="132"/>
+      <c r="N11" s="132"/>
+      <c r="O11" s="132"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
+      <c r="R11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="133"/>
       <c r="U11" s="61"/>
       <c r="V11" s="62"/>
       <c r="W11" s="62"/>
@@ -2864,28 +2883,28 @@
       <c r="AA11" s="62"/>
       <c r="AL11" s="106"/>
     </row>
-    <row r="12" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>5</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="30"/>
       <c r="E12" s="51"/>
       <c r="F12" s="3"/>
       <c r="G12" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K12" s="21"/>
       <c r="L12" s="21"/>
@@ -2899,72 +2918,72 @@
       <c r="T12" s="35"/>
       <c r="U12" s="42"/>
       <c r="V12" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X12" s="21"/>
       <c r="Y12" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z12" s="24"/>
       <c r="AA12" s="28"/>
       <c r="AB12" s="47"/>
       <c r="AC12" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD12" s="29"/>
       <c r="AE12" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF12" s="19"/>
       <c r="AG12" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH12" s="24"/>
       <c r="AI12" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ12" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK12" s="28"/>
       <c r="AL12" s="105"/>
       <c r="AM12" s="59"/>
       <c r="AN12" s="59"/>
     </row>
-    <row r="13" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>6</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="26"/>
       <c r="D13" s="30"/>
       <c r="E13" s="52"/>
       <c r="F13" s="3"/>
       <c r="G13" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L13" s="24"/>
       <c r="M13" s="24"/>
       <c r="N13" s="24"/>
       <c r="O13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P13" s="24"/>
       <c r="Q13" s="35"/>
@@ -2973,49 +2992,49 @@
       <c r="T13" s="38"/>
       <c r="U13" s="42"/>
       <c r="V13" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X13" s="21"/>
       <c r="Y13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z13" s="24"/>
       <c r="AA13" s="28"/>
       <c r="AB13" s="47"/>
       <c r="AC13" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD13" s="31"/>
       <c r="AE13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH13" s="24"/>
       <c r="AI13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ13" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK13" s="28"/>
       <c r="AL13" s="105"/>
       <c r="AM13" s="12"/>
       <c r="AN13" s="12"/>
     </row>
-    <row r="14" spans="1:40" s="2" customFormat="1" ht="18.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:40" s="2" customFormat="1" ht="18.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>7</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="30"/>
@@ -3038,7 +3057,7 @@
       <c r="U14" s="42"/>
       <c r="V14" s="30"/>
       <c r="W14" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X14" s="24"/>
       <c r="Y14" s="24"/>
@@ -3046,53 +3065,53 @@
       <c r="AA14" s="28"/>
       <c r="AB14" s="47"/>
       <c r="AC14" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD14" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE14" s="24"/>
       <c r="AF14" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG14" s="21"/>
       <c r="AH14" s="21"/>
       <c r="AI14" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ14" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK14" s="28"/>
       <c r="AL14" s="105"/>
       <c r="AM14" s="12"/>
       <c r="AN14" s="12"/>
     </row>
-    <row r="15" spans="1:40" s="63" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:40" s="63" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="120" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="130"/>
-      <c r="R15" s="130"/>
-      <c r="S15" s="130"/>
-      <c r="T15" s="122"/>
+        <v>74</v>
+      </c>
+      <c r="B15" s="131" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="132"/>
+      <c r="N15" s="132"/>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="132"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="132"/>
+      <c r="T15" s="133"/>
       <c r="U15" s="61"/>
       <c r="V15" s="62"/>
       <c r="W15" s="62"/>
@@ -3102,12 +3121,12 @@
       <c r="AA15" s="62"/>
       <c r="AL15" s="106"/>
     </row>
-    <row r="16" spans="1:40" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:40" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>8</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="30"/>
@@ -3116,22 +3135,22 @@
       <c r="G16" s="26"/>
       <c r="H16" s="27"/>
       <c r="I16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M16" s="24"/>
       <c r="N16" s="24"/>
       <c r="O16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q16" s="24"/>
       <c r="R16" s="24"/>
@@ -3140,10 +3159,10 @@
       <c r="U16" s="42"/>
       <c r="V16" s="30"/>
       <c r="W16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y16" s="24"/>
       <c r="Z16" s="24"/>
@@ -3151,33 +3170,33 @@
       <c r="AB16" s="47"/>
       <c r="AC16" s="26"/>
       <c r="AD16" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
       <c r="AG16" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH16" s="24"/>
       <c r="AI16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK16" s="28"/>
-      <c r="AL16" s="139" t="s">
-        <v>90</v>
+      <c r="AL16" s="122" t="s">
+        <v>82</v>
       </c>
       <c r="AM16" s="103"/>
       <c r="AN16" s="103"/>
     </row>
-    <row r="17" spans="1:40" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:40" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>9</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="32"/>
       <c r="D17" s="21"/>
@@ -3186,22 +3205,22 @@
       <c r="G17" s="26"/>
       <c r="H17" s="27"/>
       <c r="I17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M17" s="24"/>
       <c r="N17" s="24"/>
       <c r="O17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q17" s="24"/>
       <c r="R17" s="24"/>
@@ -3210,10 +3229,10 @@
       <c r="U17" s="42"/>
       <c r="V17" s="30"/>
       <c r="W17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y17" s="24"/>
       <c r="Z17" s="24"/>
@@ -3221,31 +3240,31 @@
       <c r="AB17" s="47"/>
       <c r="AC17" s="26"/>
       <c r="AD17" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE17" s="19"/>
       <c r="AF17" s="19"/>
       <c r="AG17" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH17" s="24"/>
       <c r="AI17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ17" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK17" s="28"/>
-      <c r="AL17" s="139"/>
+      <c r="AL17" s="122"/>
       <c r="AM17" s="103"/>
       <c r="AN17" s="103"/>
     </row>
-    <row r="18" spans="1:40" s="2" customFormat="1" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:40" s="2" customFormat="1" ht="30.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>10</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="30"/>
@@ -3254,20 +3273,20 @@
       <c r="G18" s="26"/>
       <c r="H18" s="30"/>
       <c r="I18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J18" s="24"/>
       <c r="K18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L18" s="24"/>
       <c r="M18" s="24"/>
       <c r="N18" s="24"/>
       <c r="O18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q18" s="21"/>
       <c r="R18" s="34"/>
@@ -3276,7 +3295,7 @@
       <c r="U18" s="42"/>
       <c r="V18" s="30"/>
       <c r="W18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X18" s="24"/>
       <c r="Y18" s="24"/>
@@ -3284,34 +3303,34 @@
       <c r="AA18" s="28"/>
       <c r="AB18" s="47"/>
       <c r="AC18" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE18" s="24"/>
       <c r="AF18" s="24"/>
       <c r="AG18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH18" s="24"/>
       <c r="AI18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ18" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK18" s="28"/>
       <c r="AL18" s="105"/>
       <c r="AM18" s="12"/>
       <c r="AN18" s="12"/>
     </row>
-    <row r="19" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>11</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="26"/>
       <c r="D19" s="30"/>
@@ -3320,16 +3339,16 @@
       <c r="G19" s="26"/>
       <c r="H19" s="30"/>
       <c r="I19" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J19" s="24"/>
       <c r="K19" s="24"/>
       <c r="L19" s="24"/>
       <c r="M19" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N19" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O19" s="24"/>
       <c r="P19" s="24"/>
@@ -3340,7 +3359,7 @@
       <c r="U19" s="42"/>
       <c r="V19" s="30"/>
       <c r="W19" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X19" s="24"/>
       <c r="Y19" s="24"/>
@@ -3350,30 +3369,30 @@
       <c r="AC19" s="26"/>
       <c r="AD19" s="31"/>
       <c r="AE19" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF19" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG19" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH19" s="24"/>
       <c r="AI19" s="21"/>
       <c r="AJ19" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK19" s="28"/>
       <c r="AL19" s="105"/>
       <c r="AM19" s="12"/>
       <c r="AN19" s="12"/>
     </row>
-    <row r="20" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>12</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="26"/>
       <c r="D20" s="30"/>
@@ -3382,22 +3401,22 @@
       <c r="G20" s="26"/>
       <c r="H20" s="27"/>
       <c r="I20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M20" s="24"/>
       <c r="N20" s="24"/>
       <c r="O20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q20" s="31"/>
       <c r="R20" s="31"/>
@@ -3406,7 +3425,7 @@
       <c r="U20" s="42"/>
       <c r="V20" s="30"/>
       <c r="W20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X20" s="21"/>
       <c r="Y20" s="24"/>
@@ -3416,28 +3435,28 @@
       <c r="AC20" s="26"/>
       <c r="AD20" s="31"/>
       <c r="AE20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF20" s="24"/>
       <c r="AG20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH20" s="24"/>
       <c r="AI20" s="24"/>
       <c r="AJ20" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK20" s="28"/>
       <c r="AL20" s="105"/>
       <c r="AM20" s="12"/>
       <c r="AN20" s="12"/>
     </row>
-    <row r="21" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>13</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="30"/>
@@ -3457,72 +3476,72 @@
       <c r="R21" s="24"/>
       <c r="S21" s="35"/>
       <c r="T21" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U21" s="42"/>
       <c r="V21" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X21" s="21"/>
       <c r="Y21" s="24"/>
       <c r="Z21" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA21" s="28"/>
       <c r="AB21" s="47"/>
       <c r="AC21" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD21" s="24"/>
       <c r="AE21" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF21" s="24"/>
       <c r="AG21" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH21" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI21" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ21" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK21" s="28"/>
       <c r="AL21" s="105"/>
       <c r="AM21" s="12"/>
       <c r="AN21" s="12"/>
     </row>
-    <row r="22" spans="1:40" s="63" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:40" s="63" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="120" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="130"/>
-      <c r="D22" s="130"/>
-      <c r="E22" s="130"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="130"/>
-      <c r="I22" s="130"/>
-      <c r="J22" s="130"/>
-      <c r="K22" s="130"/>
-      <c r="L22" s="130"/>
-      <c r="M22" s="130"/>
-      <c r="N22" s="130"/>
-      <c r="O22" s="130"/>
-      <c r="P22" s="130"/>
-      <c r="Q22" s="130"/>
-      <c r="R22" s="130"/>
-      <c r="S22" s="130"/>
-      <c r="T22" s="122"/>
+        <v>74</v>
+      </c>
+      <c r="B22" s="131" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="132"/>
+      <c r="D22" s="132"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="132"/>
+      <c r="J22" s="132"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
+      <c r="M22" s="132"/>
+      <c r="N22" s="132"/>
+      <c r="O22" s="132"/>
+      <c r="P22" s="132"/>
+      <c r="Q22" s="132"/>
+      <c r="R22" s="132"/>
+      <c r="S22" s="132"/>
+      <c r="T22" s="133"/>
       <c r="U22" s="61"/>
       <c r="V22" s="62"/>
       <c r="W22" s="62"/>
@@ -3532,12 +3551,12 @@
       <c r="AA22" s="62"/>
       <c r="AL22" s="106"/>
     </row>
-    <row r="23" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>14</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C23" s="26"/>
       <c r="D23" s="30"/>
@@ -3560,7 +3579,7 @@
       <c r="U23" s="42"/>
       <c r="V23" s="30"/>
       <c r="W23" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X23" s="24"/>
       <c r="Y23" s="24"/>
@@ -3568,11 +3587,11 @@
       <c r="AA23" s="28"/>
       <c r="AB23" s="47"/>
       <c r="AC23" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD23" s="31"/>
       <c r="AE23" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF23" s="24"/>
       <c r="AG23" s="24"/>
@@ -3584,12 +3603,12 @@
       <c r="AM23" s="12"/>
       <c r="AN23" s="12"/>
     </row>
-    <row r="24" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>15</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="30"/>
@@ -3609,32 +3628,32 @@
       <c r="R24" s="24"/>
       <c r="S24" s="35"/>
       <c r="T24" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U24" s="42"/>
       <c r="V24" s="30"/>
       <c r="W24" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X24" s="24"/>
       <c r="Y24" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z24" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA24" s="28"/>
       <c r="AB24" s="47"/>
       <c r="AC24" s="26"/>
       <c r="AD24" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE24" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF24" s="24"/>
       <c r="AG24" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH24" s="24"/>
       <c r="AI24" s="24"/>
@@ -3644,12 +3663,12 @@
       <c r="AM24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
-    <row r="25" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>16</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="30"/>
@@ -3669,32 +3688,32 @@
       <c r="R25" s="24"/>
       <c r="S25" s="35"/>
       <c r="T25" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U25" s="42"/>
       <c r="V25" s="30"/>
       <c r="W25" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X25" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y25" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z25" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA25" s="28"/>
       <c r="AB25" s="47"/>
       <c r="AC25" s="26"/>
       <c r="AD25" s="21"/>
       <c r="AE25" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF25" s="24"/>
       <c r="AG25" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH25" s="24"/>
       <c r="AI25" s="24"/>
@@ -3704,12 +3723,12 @@
       <c r="AM25" s="12"/>
       <c r="AN25" s="12"/>
     </row>
-    <row r="26" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>17</v>
       </c>
       <c r="B26" s="70" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="30"/>
@@ -3719,7 +3738,7 @@
       <c r="H26" s="30"/>
       <c r="I26" s="24"/>
       <c r="J26" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K26" s="24"/>
       <c r="L26" s="24"/>
@@ -3728,21 +3747,21 @@
       <c r="O26" s="24"/>
       <c r="P26" s="24"/>
       <c r="Q26" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R26" s="24"/>
       <c r="S26" s="35"/>
       <c r="T26" s="35"/>
       <c r="U26" s="42"/>
       <c r="V26" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X26" s="21"/>
       <c r="Y26" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z26" s="24"/>
       <c r="AA26" s="28"/>
@@ -3751,29 +3770,29 @@
       <c r="AD26" s="24"/>
       <c r="AE26" s="24"/>
       <c r="AF26" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG26" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH26" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI26" s="21"/>
       <c r="AJ26" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK26" s="28"/>
       <c r="AL26" s="105"/>
       <c r="AM26" s="12"/>
       <c r="AN26" s="12"/>
     </row>
-    <row r="27" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>18</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="30"/>
@@ -3790,17 +3809,17 @@
       <c r="O27" s="24"/>
       <c r="P27" s="24"/>
       <c r="Q27" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R27" s="21"/>
       <c r="S27" s="29"/>
       <c r="T27" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U27" s="42"/>
       <c r="V27" s="30"/>
       <c r="W27" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X27" s="21"/>
       <c r="Y27" s="24"/>
@@ -3808,15 +3827,15 @@
       <c r="AA27" s="28"/>
       <c r="AB27" s="47"/>
       <c r="AC27" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD27" s="24"/>
       <c r="AE27" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF27" s="24"/>
       <c r="AG27" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH27" s="24"/>
       <c r="AI27" s="24"/>
@@ -3826,12 +3845,12 @@
       <c r="AM27" s="12"/>
       <c r="AN27" s="12"/>
     </row>
-    <row r="28" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>19</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="30"/>
@@ -3851,53 +3870,53 @@
       <c r="R28" s="24"/>
       <c r="S28" s="35"/>
       <c r="T28" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U28" s="42"/>
       <c r="V28" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W28" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X28" s="24"/>
       <c r="Y28" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z28" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA28" s="28"/>
       <c r="AB28" s="47"/>
       <c r="AC28" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD28" s="24"/>
       <c r="AE28" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF28" s="24"/>
       <c r="AG28" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH28" s="24"/>
       <c r="AI28" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ28" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK28" s="28"/>
       <c r="AL28" s="105"/>
       <c r="AM28" s="12"/>
       <c r="AN28" s="12"/>
     </row>
-    <row r="29" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>20</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="30"/>
@@ -3917,30 +3936,30 @@
       <c r="R29" s="24"/>
       <c r="S29" s="35"/>
       <c r="T29" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U29" s="42"/>
       <c r="V29" s="30"/>
       <c r="W29" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X29" s="24"/>
       <c r="Y29" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z29" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA29" s="28"/>
       <c r="AB29" s="47"/>
       <c r="AC29" s="26"/>
       <c r="AD29" s="24"/>
       <c r="AE29" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF29" s="24"/>
       <c r="AG29" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH29" s="24"/>
       <c r="AI29" s="24"/>
@@ -3950,12 +3969,12 @@
       <c r="AM29" s="12"/>
       <c r="AN29" s="12"/>
     </row>
-    <row r="30" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>21</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="30"/>
@@ -3975,30 +3994,30 @@
       <c r="R30" s="21"/>
       <c r="S30" s="29"/>
       <c r="T30" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U30" s="42"/>
       <c r="V30" s="30"/>
       <c r="W30" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X30" s="24"/>
       <c r="Y30" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z30" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA30" s="28"/>
       <c r="AB30" s="47"/>
       <c r="AC30" s="26"/>
       <c r="AD30" s="24"/>
       <c r="AE30" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF30" s="24"/>
       <c r="AG30" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH30" s="24"/>
       <c r="AI30" s="24"/>
@@ -4008,12 +4027,12 @@
       <c r="AM30" s="12"/>
       <c r="AN30" s="12"/>
     </row>
-    <row r="31" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:40" s="2" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>22</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="30"/>
@@ -4035,10 +4054,10 @@
       <c r="T31" s="35"/>
       <c r="U31" s="42"/>
       <c r="V31" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W31" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X31" s="21"/>
       <c r="Y31" s="24"/>
@@ -4047,29 +4066,31 @@
       <c r="AB31" s="47"/>
       <c r="AC31" s="26"/>
       <c r="AD31" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE31" s="24"/>
       <c r="AF31" s="24"/>
       <c r="AG31" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH31" s="24"/>
       <c r="AI31" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ31" s="24"/>
       <c r="AK31" s="28"/>
-      <c r="AL31" s="105"/>
+      <c r="AL31" s="108" t="s">
+        <v>94</v>
+      </c>
       <c r="AM31" s="12"/>
       <c r="AN31" s="12"/>
     </row>
-    <row r="32" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>23</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="30"/>
@@ -4089,12 +4110,12 @@
       <c r="R32" s="24"/>
       <c r="S32" s="35"/>
       <c r="T32" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U32" s="43"/>
       <c r="V32" s="27"/>
       <c r="W32" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X32" s="21"/>
       <c r="Y32" s="24"/>
@@ -4104,30 +4125,30 @@
       <c r="AC32" s="26"/>
       <c r="AD32" s="21"/>
       <c r="AE32" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF32" s="24"/>
       <c r="AG32" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH32" s="24"/>
       <c r="AI32" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ32" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK32" s="28"/>
       <c r="AL32" s="105"/>
       <c r="AM32" s="12"/>
       <c r="AN32" s="12"/>
     </row>
-    <row r="33" spans="1:40" s="2" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:40" s="2" customFormat="1" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>24</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C33" s="109"/>
       <c r="D33" s="110"/>
@@ -4147,55 +4168,55 @@
       <c r="R33" s="112"/>
       <c r="S33" s="113"/>
       <c r="T33" s="114" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U33" s="115"/>
       <c r="V33" s="116" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W33" s="117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X33" s="112"/>
       <c r="Y33" s="117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z33" s="117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA33" s="118"/>
       <c r="AB33" s="119"/>
       <c r="AC33" s="109"/>
       <c r="AD33" s="112"/>
       <c r="AE33" s="117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF33" s="117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG33" s="117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH33" s="112"/>
       <c r="AI33" s="117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ33" s="117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK33" s="118"/>
       <c r="AL33" s="108" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM33" s="12"/>
       <c r="AN33" s="12"/>
     </row>
-    <row r="34" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>25</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="30"/>
@@ -4215,17 +4236,17 @@
       <c r="R34" s="24"/>
       <c r="S34" s="35"/>
       <c r="T34" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U34" s="41"/>
       <c r="V34" s="30"/>
       <c r="W34" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X34" s="21"/>
       <c r="Y34" s="24"/>
       <c r="Z34" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA34" s="28"/>
       <c r="AB34" s="47"/>
@@ -4233,29 +4254,29 @@
       <c r="AD34" s="24"/>
       <c r="AE34" s="21"/>
       <c r="AF34" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG34" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH34" s="24"/>
       <c r="AI34" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ34" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK34" s="28"/>
       <c r="AL34" s="105"/>
       <c r="AM34" s="12"/>
       <c r="AN34" s="12"/>
     </row>
-    <row r="35" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>26</v>
       </c>
       <c r="B35" s="50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="30"/>
@@ -4275,19 +4296,19 @@
       <c r="R35" s="24"/>
       <c r="S35" s="35"/>
       <c r="T35" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U35" s="42"/>
       <c r="V35" s="30"/>
       <c r="W35" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X35" s="21"/>
       <c r="Y35" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z35" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA35" s="36"/>
       <c r="AB35" s="47"/>
@@ -4295,29 +4316,29 @@
       <c r="AD35" s="24"/>
       <c r="AE35" s="24"/>
       <c r="AF35" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG35" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH35" s="21"/>
       <c r="AI35" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ35" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK35" s="28"/>
       <c r="AL35" s="105"/>
       <c r="AM35" s="12"/>
       <c r="AN35" s="12"/>
     </row>
-    <row r="36" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>27</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="30"/>
@@ -4340,61 +4361,61 @@
       <c r="U36" s="42"/>
       <c r="V36" s="30"/>
       <c r="W36" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X36" s="21"/>
       <c r="Y36" s="21"/>
       <c r="Z36" s="21"/>
       <c r="AA36" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB36" s="47"/>
       <c r="AC36" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD36" s="24"/>
       <c r="AE36" s="24"/>
       <c r="AF36" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG36" s="21"/>
       <c r="AH36" s="21"/>
       <c r="AI36" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ36" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK36" s="28"/>
       <c r="AL36" s="105"/>
       <c r="AM36" s="12"/>
       <c r="AN36" s="12"/>
     </row>
-    <row r="37" spans="1:40" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:40" s="63" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="60" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="120" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="121"/>
-      <c r="D37" s="121"/>
-      <c r="E37" s="121"/>
-      <c r="F37" s="121"/>
-      <c r="G37" s="121"/>
-      <c r="H37" s="121"/>
-      <c r="I37" s="121"/>
-      <c r="J37" s="121"/>
-      <c r="K37" s="121"/>
-      <c r="L37" s="121"/>
-      <c r="M37" s="121"/>
-      <c r="N37" s="121"/>
-      <c r="O37" s="121"/>
-      <c r="P37" s="121"/>
-      <c r="Q37" s="121"/>
-      <c r="R37" s="121"/>
-      <c r="S37" s="121"/>
-      <c r="T37" s="122"/>
+        <v>76</v>
+      </c>
+      <c r="B37" s="131" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="132"/>
+      <c r="D37" s="132"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="132"/>
+      <c r="H37" s="132"/>
+      <c r="I37" s="132"/>
+      <c r="J37" s="132"/>
+      <c r="K37" s="132"/>
+      <c r="L37" s="132"/>
+      <c r="M37" s="132"/>
+      <c r="N37" s="132"/>
+      <c r="O37" s="132"/>
+      <c r="P37" s="132"/>
+      <c r="Q37" s="132"/>
+      <c r="R37" s="132"/>
+      <c r="S37" s="132"/>
+      <c r="T37" s="133"/>
       <c r="U37" s="62"/>
       <c r="V37" s="62"/>
       <c r="W37" s="62"/>
@@ -4403,12 +4424,12 @@
       <c r="Z37" s="62"/>
       <c r="AL37" s="106"/>
     </row>
-    <row r="38" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>28</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C38" s="32"/>
       <c r="D38" s="21"/>
@@ -4431,7 +4452,7 @@
       <c r="U38" s="42"/>
       <c r="V38" s="30"/>
       <c r="W38" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X38" s="24"/>
       <c r="Y38" s="24"/>
@@ -4439,10 +4460,10 @@
       <c r="AA38" s="28"/>
       <c r="AB38" s="47"/>
       <c r="AC38" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD38" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE38" s="24"/>
       <c r="AF38" s="24"/>
@@ -4455,12 +4476,12 @@
       <c r="AM38" s="12"/>
       <c r="AN38" s="12"/>
     </row>
-    <row r="39" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>29</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C39" s="32"/>
       <c r="D39" s="27"/>
@@ -4501,12 +4522,12 @@
       <c r="AM39" s="12"/>
       <c r="AN39" s="12"/>
     </row>
-    <row r="40" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>30</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C40" s="26"/>
       <c r="D40" s="30"/>
@@ -4529,44 +4550,44 @@
       <c r="U40" s="42"/>
       <c r="V40" s="30"/>
       <c r="W40" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X40" s="21"/>
       <c r="Y40" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z40" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA40" s="28"/>
       <c r="AB40" s="47"/>
       <c r="AC40" s="26"/>
       <c r="AD40" s="31"/>
       <c r="AE40" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF40" s="24"/>
       <c r="AG40" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH40" s="24"/>
       <c r="AI40" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ40" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK40" s="28"/>
       <c r="AL40" s="105"/>
       <c r="AM40" s="12"/>
       <c r="AN40" s="12"/>
     </row>
-    <row r="41" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>31</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="30"/>
@@ -4589,31 +4610,31 @@
       <c r="U41" s="42"/>
       <c r="V41" s="30"/>
       <c r="W41" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X41" s="24"/>
       <c r="Y41" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z41" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA41" s="28"/>
       <c r="AB41" s="47"/>
       <c r="AC41" s="26"/>
       <c r="AD41" s="24"/>
       <c r="AE41" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF41" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG41" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH41" s="24"/>
       <c r="AI41" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ41" s="24"/>
       <c r="AK41" s="28"/>
@@ -4621,12 +4642,12 @@
       <c r="AM41" s="12"/>
       <c r="AN41" s="12"/>
     </row>
-    <row r="42" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>32</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C42" s="26"/>
       <c r="D42" s="30"/>
@@ -4646,57 +4667,57 @@
       <c r="R42" s="24"/>
       <c r="S42" s="35"/>
       <c r="T42" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U42" s="42"/>
       <c r="V42" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X42" s="21"/>
       <c r="Y42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA42" s="28"/>
       <c r="AB42" s="47"/>
       <c r="AC42" s="26"/>
       <c r="AD42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ42" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK42" s="28"/>
       <c r="AL42" s="105"/>
       <c r="AM42" s="12"/>
       <c r="AN42" s="12"/>
     </row>
-    <row r="43" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>33</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="30"/>
@@ -4718,13 +4739,13 @@
       <c r="T43" s="35"/>
       <c r="U43" s="42"/>
       <c r="V43" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W43" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X43" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y43" s="24"/>
       <c r="Z43" s="24"/>
@@ -4734,13 +4755,13 @@
       <c r="AD43" s="24"/>
       <c r="AE43" s="24"/>
       <c r="AF43" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG43" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH43" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI43" s="21"/>
       <c r="AJ43" s="21"/>
@@ -4749,12 +4770,12 @@
       <c r="AM43" s="12"/>
       <c r="AN43" s="12"/>
     </row>
-    <row r="44" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>34</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C44" s="32"/>
       <c r="D44" s="27"/>
@@ -4776,10 +4797,10 @@
       <c r="T44" s="35"/>
       <c r="U44" s="42"/>
       <c r="V44" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W44" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X44" s="21"/>
       <c r="Y44" s="24"/>
@@ -4787,36 +4808,36 @@
       <c r="AA44" s="28"/>
       <c r="AB44" s="47"/>
       <c r="AC44" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD44" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE44" s="24"/>
       <c r="AF44" s="21"/>
       <c r="AG44" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH44" s="24"/>
       <c r="AI44" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ44" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK44" s="28"/>
       <c r="AL44" s="105" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AM44" s="12"/>
       <c r="AN44" s="12"/>
     </row>
-    <row r="45" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>35</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C45" s="26"/>
       <c r="D45" s="30"/>
@@ -4839,7 +4860,7 @@
       <c r="U45" s="42"/>
       <c r="V45" s="30"/>
       <c r="W45" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X45" s="24"/>
       <c r="Y45" s="24"/>
@@ -4859,28 +4880,28 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="12"/>
     </row>
-    <row r="46" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>36</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C46" s="32"/>
       <c r="D46" s="21"/>
       <c r="E46" s="51"/>
       <c r="F46" s="3"/>
       <c r="G46" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J46" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K46" s="24"/>
       <c r="L46" s="24"/>
@@ -4894,10 +4915,10 @@
       <c r="T46" s="35"/>
       <c r="U46" s="42"/>
       <c r="V46" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W46" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X46" s="21"/>
       <c r="Y46" s="24"/>
@@ -4905,34 +4926,34 @@
       <c r="AA46" s="28"/>
       <c r="AB46" s="47"/>
       <c r="AC46" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD46" s="31"/>
       <c r="AE46" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF46" s="24"/>
       <c r="AG46" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH46" s="24"/>
       <c r="AI46" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ46" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK46" s="28"/>
       <c r="AL46" s="105"/>
       <c r="AM46" s="12"/>
       <c r="AN46" s="12"/>
     </row>
-    <row r="47" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>37</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C47" s="26"/>
       <c r="D47" s="30"/>
@@ -4952,47 +4973,47 @@
       <c r="R47" s="24"/>
       <c r="S47" s="35"/>
       <c r="T47" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U47" s="42"/>
       <c r="V47" s="30"/>
       <c r="W47" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X47" s="21"/>
       <c r="Y47" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z47" s="24"/>
       <c r="AA47" s="28"/>
       <c r="AB47" s="47"/>
       <c r="AC47" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD47" s="24"/>
       <c r="AE47" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF47" s="24"/>
       <c r="AG47" s="24"/>
       <c r="AH47" s="24"/>
       <c r="AI47" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ47" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK47" s="28"/>
       <c r="AL47" s="105"/>
       <c r="AM47" s="12"/>
       <c r="AN47" s="12"/>
     </row>
-    <row r="48" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>38</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="30"/>
@@ -5012,18 +5033,18 @@
       <c r="R48" s="24"/>
       <c r="S48" s="35"/>
       <c r="T48" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U48" s="42"/>
       <c r="V48" s="27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W48" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X48" s="21"/>
       <c r="Y48" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z48" s="24"/>
       <c r="AA48" s="28"/>
@@ -5035,66 +5056,66 @@
       <c r="AG48" s="24"/>
       <c r="AH48" s="24"/>
       <c r="AI48" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ48" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK48" s="28"/>
       <c r="AL48" s="105"/>
       <c r="AM48" s="12"/>
       <c r="AN48" s="12"/>
     </row>
-    <row r="49" spans="1:40" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:40" s="63" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="87" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" s="131" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" s="132"/>
-      <c r="D49" s="132"/>
-      <c r="E49" s="132"/>
-      <c r="F49" s="132"/>
-      <c r="G49" s="132"/>
-      <c r="H49" s="132"/>
-      <c r="I49" s="132"/>
-      <c r="J49" s="132"/>
-      <c r="K49" s="132"/>
-      <c r="L49" s="132"/>
-      <c r="M49" s="132"/>
-      <c r="N49" s="132"/>
-      <c r="O49" s="132"/>
-      <c r="P49" s="132"/>
-      <c r="Q49" s="132"/>
-      <c r="R49" s="132"/>
-      <c r="S49" s="132"/>
-      <c r="T49" s="132"/>
-      <c r="U49" s="132"/>
-      <c r="V49" s="132"/>
-      <c r="W49" s="132"/>
-      <c r="X49" s="132"/>
-      <c r="Y49" s="132"/>
-      <c r="Z49" s="132"/>
-      <c r="AA49" s="132"/>
-      <c r="AB49" s="132"/>
-      <c r="AC49" s="132"/>
-      <c r="AD49" s="132"/>
-      <c r="AE49" s="132"/>
-      <c r="AF49" s="132"/>
-      <c r="AG49" s="132"/>
-      <c r="AH49" s="132"/>
-      <c r="AI49" s="132"/>
-      <c r="AJ49" s="132"/>
-      <c r="AK49" s="133"/>
+        <v>76</v>
+      </c>
+      <c r="B49" s="138" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="139"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="139"/>
+      <c r="F49" s="139"/>
+      <c r="G49" s="139"/>
+      <c r="H49" s="139"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="139"/>
+      <c r="K49" s="139"/>
+      <c r="L49" s="139"/>
+      <c r="M49" s="139"/>
+      <c r="N49" s="139"/>
+      <c r="O49" s="139"/>
+      <c r="P49" s="139"/>
+      <c r="Q49" s="139"/>
+      <c r="R49" s="139"/>
+      <c r="S49" s="139"/>
+      <c r="T49" s="139"/>
+      <c r="U49" s="139"/>
+      <c r="V49" s="139"/>
+      <c r="W49" s="139"/>
+      <c r="X49" s="139"/>
+      <c r="Y49" s="139"/>
+      <c r="Z49" s="139"/>
+      <c r="AA49" s="139"/>
+      <c r="AB49" s="139"/>
+      <c r="AC49" s="139"/>
+      <c r="AD49" s="139"/>
+      <c r="AE49" s="139"/>
+      <c r="AF49" s="139"/>
+      <c r="AG49" s="139"/>
+      <c r="AH49" s="139"/>
+      <c r="AI49" s="139"/>
+      <c r="AJ49" s="139"/>
+      <c r="AK49" s="140"/>
       <c r="AL49" s="106"/>
     </row>
-    <row r="50" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:40" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="88">
         <v>39</v>
       </c>
       <c r="B50" s="89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C50" s="90"/>
       <c r="D50" s="91"/>
@@ -5114,12 +5135,12 @@
       <c r="R50" s="98"/>
       <c r="S50" s="99"/>
       <c r="T50" s="100" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U50" s="101"/>
       <c r="V50" s="91"/>
       <c r="W50" s="96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X50" s="96"/>
       <c r="Y50" s="97"/>
@@ -5127,42 +5148,42 @@
       <c r="AA50" s="102"/>
       <c r="AB50" s="48"/>
       <c r="AC50" s="94" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD50" s="96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE50" s="96"/>
       <c r="AF50" s="97"/>
       <c r="AG50" s="96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH50" s="97"/>
       <c r="AI50" s="96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ50" s="96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK50" s="92"/>
       <c r="AL50" s="107"/>
       <c r="AM50" s="12"/>
       <c r="AN50" s="12"/>
     </row>
-    <row r="51" spans="1:40" ht="18.3" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:40" ht="18.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="AK51" s="19"/>
     </row>
-    <row r="52" spans="1:40" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:40" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="8"/>
       <c r="B52" s="58" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="57"/>
       <c r="G52" s="57" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H52" s="23"/>
       <c r="I52" s="23"/>
@@ -5195,10 +5216,10 @@
       <c r="AJ52" s="23"/>
       <c r="AK52" s="23"/>
     </row>
-    <row r="53" spans="1:40" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:40" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A53" s="8"/>
       <c r="B53" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C53" s="12"/>
       <c r="D53" s="12"/>
@@ -5235,10 +5256,10 @@
       <c r="AJ53" s="23"/>
       <c r="AK53" s="23"/>
     </row>
-    <row r="54" spans="1:40" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:40" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A54" s="8"/>
       <c r="B54" s="12" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C54" s="12"/>
       <c r="D54" s="12"/>
@@ -5276,10 +5297,10 @@
       <c r="AJ54" s="23"/>
       <c r="AK54" s="23"/>
     </row>
-    <row r="55" spans="1:40" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:40" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A55" s="8"/>
       <c r="B55" s="12" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C55" s="12"/>
       <c r="D55" s="12"/>
@@ -5317,10 +5338,10 @@
       <c r="AJ55" s="23"/>
       <c r="AK55" s="23"/>
     </row>
-    <row r="56" spans="1:40" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:40" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="8"/>
       <c r="B56" s="12" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C56" s="12"/>
       <c r="D56" s="12"/>
@@ -5357,17 +5378,24 @@
       <c r="AJ56" s="23"/>
       <c r="AK56" s="8"/>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B57" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="K57" s="123"/>
-      <c r="L57" s="123"/>
-      <c r="M57" s="123"/>
-      <c r="N57" s="123"/>
+        <v>89</v>
+      </c>
+      <c r="K57" s="134"/>
+      <c r="L57" s="134"/>
+      <c r="M57" s="134"/>
+      <c r="N57" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B37:T37"/>
+    <mergeCell ref="K57:N57"/>
+    <mergeCell ref="B22:T22"/>
+    <mergeCell ref="B49:AK49"/>
+    <mergeCell ref="B6:T6"/>
+    <mergeCell ref="B11:T11"/>
+    <mergeCell ref="B15:T15"/>
     <mergeCell ref="AL4:AL5"/>
     <mergeCell ref="AL16:AL17"/>
     <mergeCell ref="A1:AE1"/>
@@ -5378,15 +5406,8 @@
     <mergeCell ref="V4:AA4"/>
     <mergeCell ref="AC4:AK4"/>
     <mergeCell ref="G4:T4"/>
-    <mergeCell ref="B37:T37"/>
-    <mergeCell ref="K57:N57"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B22:T22"/>
-    <mergeCell ref="B49:AK49"/>
-    <mergeCell ref="B6:T6"/>
-    <mergeCell ref="B11:T11"/>
-    <mergeCell ref="B15:T15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.14000000000000001" header="0.2" footer="0.1"/>
